--- a/business_forms/031_personal_protective_equipment_compliance_audit_form--business_forms.xlsx
+++ b/business_forms/031_personal_protective_equipment_compliance_audit_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ppe_equipment_type</t>
+          <t>Type of PPE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>safety_helmet</t>
+          <t>Safety Helmet</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>safety_shoes</t>
+          <t>Safety Shoes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>safety_gloves</t>
+          <t>Safety Gloves</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>safety_glasses</t>
+          <t>safety_goggles</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>safety_glasses</t>
+          <t>Safety Goggles</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>safety_goggles</t>
+          <t>safety_monitor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>safety_goggles</t>
+          <t>Safety Monitor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>safety_monitor</t>
+          <t>safety_lemon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>safety_monitor</t>
+          <t>Safety Lemon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>safety_lemon</t>
+          <t>safety_lemon_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>safety_lemon</t>
+          <t>Safety Lemon 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>safety_lemon_2</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>safety_lemon_2</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,40 +745,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>safety_equipment_inspection_frequency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Safety Equipment Inspection Frequency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_frequency</t>
+          <t>safety_equipment_inspection_last_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_frequency</t>
+          <t>Safety Equipment Inspection Last Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_date</t>
+          <t>safety_equipment_inspection_next_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_date</t>
+          <t>Safety Equipment Inspection Next Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_next_date</t>
+          <t>safety_equipment_inspection_completed_by</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_next_date</t>
+          <t>Safety Equipment Inspection Completed By</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completd_by</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completd_by</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hard_hat,_safety_glasses,_earplugs</t>
+          <t>hard_hat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hard hat, Safety glasses, Earplugs</t>
+          <t>Hard hat</t>
         </is>
       </c>
     </row>
@@ -1148,36 +918,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>safety_glasses</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Safety glasses</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>safety_helmet_choices</t>
+          <t>ppe_equipment_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes,_no</t>
+          <t>earplugs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes, No</t>
+          <t>Earplugs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>safety_helmet_choices</t>
+          <t>ppe_equipment_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,51 +964,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>safety_glasses_choices</t>
+          <t>safety_helmet_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes,_no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes, No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>safety_glasses_choices</t>
+          <t>safety_helmet_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>safety_goggles_choices</t>
+          <t>safety_helmet_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes,_no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes, No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,36 +1020,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>safety_monitor_choices</t>
+          <t>safety_goggles_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes,_no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes, No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>safety_monitor_choices</t>
+          <t>safety_goggles_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,194 +1066,194 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_frequency_choices</t>
+          <t>safety_monitor_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>daily,_weekly,_monthly</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Daily, Weekly, Monthly</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_frequency_choices</t>
+          <t>safety_monitor_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
+          <t>safety_monitor_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
+          <t>safety_equipment_inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completd_by_choices</t>
+          <t>safety_equipment_inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completd_by_choices</t>
+          <t>safety_equipment_inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
+          <t>safety_equipment_inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
+          <t>safety_equipment_inspection_completed_by_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
+          <t>safety_equipment_inspection_completed_by_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
+          <t>safety_equipment_inspection_completed_by_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>safety_officer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Safety Officer</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
+          <t>safety_equipment_inspection_completed_by_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
+          <t>safety_equipment_inspection_completed_by_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1492,176 +1262,6 @@
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>manager,_supervisor,_safety_officer,_employee</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Manager, Supervisor, Safety Officer, Employee</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>safety_equipment_inspection_last_completed_by_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
